--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_14_R2.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_14_R2.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5087</v>
+        <v>4.935</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9213</v>
+        <v>7.3813</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.4126</v>
+        <v>-2.4462</v>
       </c>
       <c r="G2" t="n">
         <v>3.8458</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0382</v>
+        <v>0.3881</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2047</v>
+        <v>0.6647</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2429</v>
+        <v>-0.2765</v>
       </c>
       <c r="V2" t="n">
         <v>1.8608</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8336</v>
+        <v>2.0736</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2111</v>
+        <v>3.6528</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3775</v>
+        <v>-1.5791</v>
       </c>
       <c r="G3" t="n">
         <v>2.1021</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5718</v>
+        <v>0.8118</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3961</v>
+        <v>0.8377</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1757</v>
+        <v>-0.0259</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0722</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. JONES</t>
+          <t>I. CORDINIER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5988</v>
+        <v>0.3133</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0407</v>
+        <v>0.1108</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4419</v>
+        <v>0.2025</v>
       </c>
       <c r="G4" t="n">
-        <v>2.434</v>
+        <v>-0.6674</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1897</v>
+        <v>1.2198</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2443</v>
+        <v>-1.8872</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5239</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4871</v>
+        <v>1.2673</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0368</v>
+        <v>-2.0915</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08989999999999999</v>
+        <v>0.1567</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2974</v>
+        <v>-0.0476</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2075</v>
+        <v>0.2042</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8452</v>
+        <v>-0.411</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6765</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1687</v>
+        <v>-0.5056</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. HAZER</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2575</v>
+        <v>0.0348</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2044</v>
+        <v>-0.166</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9469</v>
+        <v>0.2009</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3542</v>
+        <v>-1.7711</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9832</v>
+        <v>-0.3456</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6291</v>
+        <v>-1.4255</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.287</v>
+        <v>-1.4704</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.287</v>
+        <v>0.4236</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.894</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9328</v>
+        <v>-0.3007</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3038</v>
+        <v>-0.7692</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6291</v>
+        <v>0.4685</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.2322</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0141</v>
+        <v>-0.1221</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>S. HAZER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3072</v>
+        <v>-0.1321</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.508</v>
+        <v>-1.0118</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2009</v>
+        <v>0.8797</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7711</v>
+        <v>-0.3542</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3456</v>
+        <v>-0.9832</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4255</v>
+        <v>0.6291</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.4704</v>
+        <v>-1.287</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4236</v>
+        <v>-1.287</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.894</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3007</v>
+        <v>0.9328</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7692</v>
+        <v>0.3038</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4685</v>
+        <v>0.6291</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.232</v>
+        <v>0.2221</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1098</v>
+        <v>0.2752</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1221</v>
+        <v>-0.0532</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. CORDINIER</t>
+          <t>K. JONES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6692</v>
+        <v>-0.1777</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9389</v>
+        <v>1.6003</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2697</v>
+        <v>-1.778</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6674</v>
+        <v>2.434</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2198</v>
+        <v>2.1897</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8872</v>
+        <v>0.2443</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8241000000000001</v>
+        <v>2.5239</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2673</v>
+        <v>2.4871</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0915</v>
+        <v>0.0368</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1567</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0476</v>
+        <v>-0.2974</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2042</v>
+        <v>0.2075</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3935</v>
+        <v>0.0688</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.955</v>
+        <v>0.2361</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4384</v>
+        <v>-0.1674</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.8098</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5875</v>
+        <v>0.5009</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4116</v>
+        <v>-1.3108</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0615</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3818</v>
+        <v>0.396</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5702</v>
+        <v>0.4837</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1885</v>
+        <v>-0.0876</v>
       </c>
       <c r="V8" t="n">
         <v>-1.6083</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4233</v>
+        <v>-1.3418</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3876</v>
+        <v>-1.4742</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0356</v>
+        <v>0.1324</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7059</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2104</v>
+        <v>0.2919</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6528</v>
+        <v>0.5663</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4424</v>
+        <v>-0.2743</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2968</v>
+        <v>-2.2387</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1803</v>
+        <v>-1.5591</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1165</v>
+        <v>-0.6796</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6765</v>
@@ -1234,13 +1234,13 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0688</v>
+        <v>-0.0108</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1766</v>
+        <v>0.4446</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8922</v>
+        <v>-0.4553</v>
       </c>
       <c r="V10" t="n">
         <v>1.6083</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.163</v>
+        <v>2.656599999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>7.5414</v>
+        <v>9.035</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.378200000000001</v>
+        <v>-6.378199999999999</v>
       </c>
       <c r="G11" t="n">
         <v>2.145300000000002</v>
@@ -1285,7 +1285,7 @@
         <v>-3.4129</v>
       </c>
       <c r="J11" t="n">
-        <v>4.150299999999999</v>
+        <v>4.1503</v>
       </c>
       <c r="K11" t="n">
         <v>6.744</v>
@@ -1303,22 +1303,22 @@
         <v>-0.8190999999999997</v>
       </c>
       <c r="P11" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-9.278199999999998</v>
+        <v>-9.2782</v>
       </c>
       <c r="R11" t="n">
         <v>9.2782</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3733</v>
+        <v>1.8669</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3415</v>
+        <v>3.8352</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.968</v>
+        <v>-1.9679</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3558</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.8239</v>
+        <v>3.796</v>
       </c>
       <c r="E12" t="n">
-        <v>5.1218</v>
+        <v>5.0038</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2979</v>
+        <v>-1.2079</v>
       </c>
       <c r="G12" t="n">
         <v>2.2476</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1149</v>
+        <v>1.087</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9911</v>
+        <v>0.8731</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1239</v>
+        <v>0.2139</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9304</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3231</v>
+        <v>2.3298</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2268</v>
+        <v>3.7472</v>
       </c>
       <c r="F13" t="n">
-        <v>0.09619999999999999</v>
+        <v>-1.4174</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6218</v>
+        <v>-1.3296</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.4852</v>
+        <v>-2.4538</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8633</v>
+        <v>1.1242</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.0253</v>
+        <v>-0.8214</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.2093</v>
+        <v>-1.2128</v>
       </c>
       <c r="L13" t="n">
-        <v>0.184</v>
+        <v>0.3914</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4035</v>
+        <v>-0.5082</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2759</v>
+        <v>-1.241</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6793</v>
+        <v>0.7328</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>3.9449</v>
+        <v>-0.5366</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2675</v>
+        <v>-0.0037</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6774</v>
+        <v>-0.5329</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>3.5002</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1444</v>
+        <v>4.5724</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6171</v>
+        <v>1.0884</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3934</v>
+        <v>1.1037</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7763</v>
+        <v>-0.0154</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.3296</v>
+        <v>-0.6218</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.4538</v>
+        <v>-1.4852</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1242</v>
+        <v>0.8633</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8214</v>
+        <v>-1.0253</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.2128</v>
+        <v>-1.2093</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3914</v>
+        <v>0.184</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5082</v>
+        <v>0.4035</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.241</v>
+        <v>-0.2759</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7328</v>
+        <v>0.6793</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2494</v>
+        <v>1.7102</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3576</v>
+        <v>1.1444</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8918</v>
+        <v>0.5658</v>
       </c>
       <c r="V14" t="n">
-        <v>3.5002</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>4.5724</v>
+        <v>2.1444</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. MICIC</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.08799999999999999</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.5476</v>
+        <v>1.1676</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4597</v>
+        <v>-0.1676</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0147</v>
+        <v>2.3691</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0349</v>
+        <v>2.1583</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0202</v>
+        <v>0.2108</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5261</v>
+        <v>2.7449</v>
       </c>
       <c r="K15" t="n">
-        <v>0.175</v>
+        <v>2.4773</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3511</v>
+        <v>0.2676</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5115</v>
+        <v>-0.3758</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1401</v>
+        <v>-0.319</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3713</v>
+        <v>-0.0568</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.0876</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R15" t="n">
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1595</v>
+        <v>-0.4413</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7389</v>
+        <v>-0.3299</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5794</v>
+        <v>-0.1114</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>C. MALCOLM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1002</v>
+        <v>0.4185</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4599</v>
+        <v>1.0639</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5601</v>
+        <v>-0.6455</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3691</v>
+        <v>-0.5023</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1583</v>
+        <v>0.7156</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2108</v>
+        <v>-1.218</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7449</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4773</v>
+        <v>1.4956</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2676</v>
+        <v>-2.2118</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3758</v>
+        <v>0.2139</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.319</v>
+        <v>-0.78</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0568</v>
+        <v>0.9939</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5415</v>
+        <v>0.7431</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0376</v>
+        <v>0.7079</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5039</v>
+        <v>0.0351</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
       <c r="W16" t="n">
         <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. MALCOLM</t>
+          <t>V. MICIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4959</v>
+        <v>-0.0809</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7101</v>
+        <v>-1.1938</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.206</v>
+        <v>1.1129</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5023</v>
+        <v>0.0147</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7156</v>
+        <v>0.0349</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.218</v>
+        <v>-0.0202</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7161999999999999</v>
+        <v>0.5261</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4956</v>
+        <v>0.175</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.2118</v>
+        <v>0.3511</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2139</v>
+        <v>-0.5115</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.78</v>
+        <v>-0.1401</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9939</v>
+        <v>-0.3713</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3917</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R17" t="n">
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1713</v>
+        <v>-0.1524</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3541</v>
+        <v>-0.3851</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5254</v>
+        <v>0.2326</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.214</v>
+        <v>2.1444</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1331</v>
+        <v>-0.9759</v>
       </c>
       <c r="E18" t="n">
         <v>-0.7248</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4083</v>
+        <v>-0.251</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9759</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3892</v>
+        <v>-0.232</v>
       </c>
       <c r="T18" t="n">
         <v>0.007900000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3971</v>
+        <v>-0.2399</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. ODIASE</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1863</v>
+        <v>-1.1596</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3424</v>
+        <v>-0.5405</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5286</v>
+        <v>-0.6191</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8477</v>
+        <v>0.0002</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.898</v>
+        <v>0.3481</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0502</v>
+        <v>-0.348</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1611</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1611</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6866</v>
+        <v>-0.6112</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7369</v>
+        <v>-0.1896</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0502</v>
+        <v>-0.4216</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0378</v>
+        <v>-0.232</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5034</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4657</v>
+        <v>-0.2399</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2876</v>
+        <v>-1.3884</v>
       </c>
       <c r="E20" t="n">
         <v>-0.4278</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8598</v>
+        <v>-0.9606</v>
       </c>
       <c r="G20" t="n">
         <v>0.0917</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.539</v>
+        <v>-0.6398</v>
       </c>
       <c r="T20" t="n">
         <v>-0.4481</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.1918</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>T. ODIASE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3168</v>
+        <v>-1.4501</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5405</v>
+        <v>-0.0115</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7763</v>
+        <v>-1.4386</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0002</v>
+        <v>-0.8477</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3481</v>
+        <v>-0.898</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.348</v>
+        <v>0.0502</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6114000000000001</v>
+        <v>-0.1611</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5377999999999999</v>
+        <v>-0.1611</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0736</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6112</v>
+        <v>-0.6866</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1896</v>
+        <v>-0.7369</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4216</v>
+        <v>0.0502</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3892</v>
+        <v>-0.226</v>
       </c>
       <c r="T21" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.1496</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3971</v>
+        <v>-0.3756</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3191</v>
+        <v>-3.1682</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0993</v>
+        <v>-2.2736</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2199</v>
+        <v>-0.8946</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5914</v>
@@ -2170,13 +2170,13 @@
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0319</v>
+        <v>0.119</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5816</v>
+        <v>0.244</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4503</v>
+        <v>-0.125</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,31 +2203,31 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1629</v>
+        <v>0.4095999999999997</v>
       </c>
       <c r="E23" t="n">
-        <v>6.914400000000002</v>
+        <v>6.914200000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.077300000000001</v>
+        <v>-6.504799999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1454</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.558400000000001</v>
+        <v>-5.5584</v>
       </c>
       <c r="I23" t="n">
         <v>3.4128</v>
       </c>
       <c r="J23" t="n">
-        <v>2.004899999999999</v>
+        <v>2.0049</v>
       </c>
       <c r="K23" t="n">
         <v>1.1859</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8190999999999999</v>
+        <v>0.8190999999999994</v>
       </c>
       <c r="M23" t="n">
         <v>-4.1502</v>
@@ -2236,10 +2236,10 @@
         <v>-6.744200000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>2.593900000000001</v>
+        <v>2.5939</v>
       </c>
       <c r="P23" t="n">
-        <v>9.999999999976694e-05</v>
+        <v>9.999999999998899e-05</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.278200000000002</v>
@@ -2248,16 +2248,16 @@
         <v>9.2783</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3734000000000002</v>
+        <v>1.1992</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9681</v>
+        <v>1.968</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.3415</v>
+        <v>-0.7691000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>1.355800000000001</v>
+        <v>1.3558</v>
       </c>
       <c r="W23" t="n">
         <v>12.2196</v>
